--- a/Ryan_Wick_Data Analytics Immersion_Ach 04_Final Report.xlsx
+++ b/Ryan_Wick_Data Analytics Immersion_Ach 04_Final Report.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ihs10539\Desktop\0. CareerFoundry\2.Data Immersion_ACH 04-Python Fundamentals for Data Analysts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ihs10539\Achievement 4 Project\05_Sent to Client\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A4A5C08-4B23-4B9F-A7A2-E820409D8E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3876F42F-AFA6-42B2-ADBE-CC7E1339422E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="808" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
